--- a/reports/raw-views/assets/tables/micro_textual_richness.xlsx
+++ b/reports/raw-views/assets/tables/micro_textual_richness.xlsx
@@ -479,42 +479,42 @@
       <c r="A2" s="1" t="inlineStr"/>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Autores</t>
+          <t>Authors</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Pares</t>
+          <t>Peers</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Analistas</t>
+          <t>Analysts</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Autores</t>
+          <t>Authors</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>Pares</t>
+          <t>Peers</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>Analistas</t>
+          <t>Analysts</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>AI</t>
         </is>
       </c>
     </row>
